--- a/data/samples/比价矩阵_测试.xlsx
+++ b/data/samples/比价矩阵_测试.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="比价矩阵" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'比价矩阵'!$A$1:$E$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +29,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF375623"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,7 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44546A"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,10 +66,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,38 +445,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>品类</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>供应商C</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>最低价</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>最低价供应商</t>
         </is>
@@ -468,7 +488,7 @@
           <t>螺钉 M4×10</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>12.5</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,7 +496,7 @@
           <t>¥12.88</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,7 +511,7 @@
           <t>电线电缆 3×2.5mm²</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>386</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -499,7 +519,7 @@
           <t>¥397.58</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>386</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -514,7 +534,7 @@
           <t>86型触摸开关</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>22.8</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,7 +542,7 @@
           <t>¥23.48</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -537,7 +557,7 @@
           <t>PVC线管 20mm</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>3.2</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -545,7 +565,7 @@
           <t>¥3.30</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -560,7 +580,7 @@
           <t>LED灯管 T8 1.2m</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>9.9</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -568,7 +588,7 @@
           <t>¥10.20</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -583,7 +603,7 @@
           <t>水泥钉 2寸</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>15.6</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -591,7 +611,7 @@
           <t>¥16.07</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -600,7 +620,29 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>生成时间：2026-09-14 15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>来源：比价矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>（色块=该行最低价）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/samples/比价矩阵_测试.xlsx
+++ b/data/samples/比价矩阵_测试.xlsx
@@ -66,16 +66,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -483,159 +486,159 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>螺钉 M4×10</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>¥12.88</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>12.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>电线电缆 3×2.5mm²</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>386</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>¥397.58</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>386</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>86型触摸开关</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>¥23.48</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>PVC线管 20mm</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>¥3.30</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>LED灯管 T8 1.2m</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>¥10.20</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>9.9</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>水泥钉 2寸</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>¥16.07</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>15.6</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>供应商A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>生成时间：2026-09-14 15:49</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>生成时间：2026-09-14 16:12</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>来源：比价矩阵</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>（色块=该行最低价）</t>
         </is>

--- a/data/samples/比价矩阵_测试.xlsx
+++ b/data/samples/比价矩阵_测试.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -626,19 +626,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>生成时间：2026-09-14 16:12</t>
+          <t>生成时间：2026-09-14 16:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>来源：比价矩阵</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>（色块=该行最低价）</t>
         </is>

--- a/data/samples/比价矩阵_测试.xlsx
+++ b/data/samples/比价矩阵_测试.xlsx
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>生成时间：2026-09-14 16:21</t>
+          <t>生成时间：2026-09-14 17:02</t>
         </is>
       </c>
     </row>
